--- a/resampling/input/accessibility_reports_generated/FHI 360_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/FHI 360_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q23" headerRowCount="1">
-  <autoFilter ref="A1:Q23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q38" headerRowCount="1">
+  <autoFilter ref="A1:Q38"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 22 wards, 39 clusters</t>
+          <t>Assigned to you: 37 wards, 39 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -843,19 +843,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Konduga; Magumeri</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -878,12 +886,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -893,7 +901,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -908,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -931,29 +939,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mujigine</t>
+          <t>Dalori</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mujigine</t>
+          <t>Tamsu Ngamdua</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -976,12 +992,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Tamsum Gamdua</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Tamsu Ngamdua</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -991,7 +1007,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Jere; Konduga</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1000,13 +1016,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1029,29 +1045,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Koshebe</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Koshebe</t>
-        </is>
-      </c>
+          <t>Boboshe</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dikwa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1074,29 +1094,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Laje</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Lege</t>
-        </is>
-      </c>
+          <t>Damakulli</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1119,29 +1143,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Masu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Masu</t>
-        </is>
-      </c>
+          <t>Gawa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dikwa; Konduga</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1164,14 +1192,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Limanti</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Limanti</t>
-        </is>
-      </c>
+          <t>Kabulawa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1179,7 +1203,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bayo; Jere; Maiduguri</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1188,13 +1212,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1217,14 +1241,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalori</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tamsu Ngamdua</t>
-        </is>
-      </c>
+          <t>Khaddamari</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1232,7 +1252,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jere; Konduga</t>
+          <t>Jere</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1241,13 +1261,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1270,14 +1290,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Khaddamari</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>Koshebe</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>No</t>
@@ -1286,13 +1302,13 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1315,37 +1331,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miye</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Masu</t>
-        </is>
-      </c>
+          <t>Laje</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Magumeri; Nganzai</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1368,14 +1372,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamsum Gamdua</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Tamsu Ngamdua</t>
-        </is>
-      </c>
+          <t>Limanti</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jere</t>
+          <t>Bayo; Jere; Maiduguri</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1416,34 +1416,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kareto</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Kareto</t>
-        </is>
-      </c>
+          <t>Loskuri</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jere; Konduga</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1461,19 +1465,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Layi</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Chamba</t>
-        </is>
-      </c>
+          <t>Ma'Afa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>No</t>
@@ -1482,13 +1482,13 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1506,19 +1506,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Futchimiram</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Kareto</t>
-        </is>
-      </c>
+          <t>Maiwa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1526,7 +1522,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gubio</t>
+          <t>Monguno; Nganzai</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1535,13 +1531,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1559,34 +1555,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zari</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Chamba</t>
-        </is>
-      </c>
+          <t>Masu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jere; Monguno; Nganzai</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1604,19 +1604,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Banowa</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bogum</t>
-        </is>
-      </c>
+          <t>Miye</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1624,7 +1620,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Abadam; Kukawa</t>
+          <t>Magumeri; Nganzai</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1633,13 +1629,13 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1657,34 +1653,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gashigar</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Gashigar</t>
-        </is>
-      </c>
+          <t>Mofio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Monguno; Nganzai</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1702,34 +1702,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fukurti</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Kareto</t>
-        </is>
-      </c>
+          <t>Mujigine</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dikwa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1747,19 +1751,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ngetra</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Kareto</t>
-        </is>
-      </c>
+          <t>Yabal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gubio</t>
+          <t>Bama; Gwoza; Konduga</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1800,19 +1800,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chamba</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Chamba</t>
-        </is>
-      </c>
+          <t>Zengebe</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>No</t>
@@ -1821,13 +1817,13 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1850,37 +1846,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gazabure</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Chamba</t>
+          <t>Zulum Umarti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gubio</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1890,23 +1878,722 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Damasak</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Damasak</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>17</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="10" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Banowa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Abadam; Guzamala; Kukawa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="10" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bogum</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Abadam</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="10" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chamba</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Degeltura</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Duji</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fukurti</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Futchimiram</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gashigar</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gubio; Guzamala</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gazabure</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gubio; Guzamala</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gudumbali West</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Abadam; Gubio; Guzamala</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kareto</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Layi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ngetra</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Zari</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gubio</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2130,7 +2817,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Masu</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2140,18 +2827,18 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_1</t>
+          <t>non_idp_NG008019_2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -2175,7 +2862,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mujigine</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2185,18 +2872,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_10</t>
+          <t>non_idp_NG008019_4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2230,7 +2917,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_11</t>
+          <t>non_idp_NG008019_6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -2265,7 +2952,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mujigine</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2275,7 +2962,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_12</t>
+          <t>non_idp_NG008019_7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -2310,7 +2997,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Limanti</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2320,7 +3007,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_13</t>
+          <t>non_idp_NG008019_supp15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2355,7 +3042,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Koshebe</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2365,7 +3052,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_14</t>
+          <t>non_idp_NG008019_supp19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -2400,7 +3087,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Limanti</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2410,7 +3097,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_15</t>
+          <t>non_idp_NG008019_supp23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -2445,7 +3132,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2455,7 +3142,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_16</t>
+          <t>non_idp_NG008019_supp25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -2490,7 +3177,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khaddamari</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2500,7 +3187,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_17</t>
+          <t>non_idp_NG008019_supp27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -2535,7 +3222,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2545,18 +3232,18 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_2</t>
+          <t>non_idp_NG008019_supp28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2580,7 +3267,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Tamsum Gamdua</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2590,18 +3277,18 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_4</t>
+          <t>non_idp_NG008019_supp3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2625,7 +3312,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2635,7 +3322,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_6</t>
+          <t>non_idp_NG008019_supp33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -2680,7 +3367,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_7</t>
+          <t>non_idp_NG008019_supp34</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2715,7 +3402,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mujigine</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2725,7 +3412,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_8</t>
+          <t>non_idp_NG008019_supp35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2755,33 +3442,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>idp_NG008023_supp1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2800,33 +3491,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>idp_NG008023_supp10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2845,33 +3540,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp2</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>idp_NG008023_supp2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,33 +3589,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tamsum Gamdua</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp3</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>idp_NG008023_supp3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2935,33 +3638,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp4</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>idp_NG008023_supp4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,25 +3687,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mobbar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Laje</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp5</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>idp_NG008023_supp5</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>6</t>
@@ -3030,28 +3741,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Layi</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>idp_NG008023_supp6</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,20 +3790,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Futchimiram</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_10</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>idp_NG008023_supp7</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>6</t>
@@ -3120,20 +3839,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_11</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>idp_NG008023_supp8</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>6</t>
@@ -3165,28 +3888,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>idp_NG008023_supp9</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,7 +3937,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3220,7 +3947,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_13</t>
+          <t>non_idp_NG008023_supp1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -3255,7 +3982,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Layi</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3265,7 +3992,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_14</t>
+          <t>non_idp_NG008023_supp11</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -3300,7 +4027,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3310,18 +4037,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_15</t>
+          <t>non_idp_NG008023_supp12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3345,7 +4072,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Layi</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3355,18 +4082,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_16</t>
+          <t>non_idp_NG008023_supp13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3390,7 +4117,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Layi</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3400,18 +4127,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_17</t>
+          <t>non_idp_NG008023_supp14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3435,7 +4162,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Layi</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3445,18 +4172,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_2</t>
+          <t>non_idp_NG008023_supp15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3480,7 +4207,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zari</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3490,7 +4217,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_3</t>
+          <t>non_idp_NG008023_supp2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3525,7 +4252,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zari</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3535,7 +4262,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_4</t>
+          <t>non_idp_NG008023_supp3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -3570,7 +4297,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3580,7 +4307,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_5</t>
+          <t>non_idp_NG008023_supp4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -3615,7 +4342,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gashigar</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3625,7 +4352,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_6</t>
+          <t>non_idp_NG008023_supp5</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -3660,7 +4387,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kareto</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3670,7 +4397,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_7</t>
+          <t>non_idp_NG008023_supp6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -3705,7 +4432,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Banowa</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3715,7 +4442,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_8</t>
+          <t>non_idp_NG008023_supp7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -3750,7 +4477,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Futchimiram</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3760,7 +4487,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_9</t>
+          <t>non_idp_NG008023_supp9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -3798,7 +4525,7 @@
     </dataValidation>
     <dataValidation sqref="M2:M40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4064,13 +4791,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEE8F6F6-10F7-43C7-BA75-D175161D0DE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1942002B-AA77-4175-96EC-2664DBAD1F55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30DF2F68-AEF2-4B7A-8C5F-B3ED5FE602D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{659B56DC-5A79-4EF6-9396-E79D268C02D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{079C3974-A325-44F6-9E5D-A44E08DB813C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B372B483-28C8-4C2A-AEB3-B6334A57C13C}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/FHI 360_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/FHI 360_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O40" headerRowCount="1">
-  <autoFilter ref="A1:O40"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P45" headerRowCount="1">
+  <autoFilter ref="A1:P45"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 37 wards, 39 clusters</t>
+          <t>Assigned to you: 37 wards, 44 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -860,10 +871,10 @@
         <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -2593,7 +2604,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2609,7 +2620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2617,16 +2628,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2657,50 +2669,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -2734,26 +2751,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-camp</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2783,26 +2805,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2822,32 +2849,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>idp_NG008019_supp1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2867,32 +2903,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>idp_NG008019_supp2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2907,37 +2952,46 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>idp_NG008019_supp3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2952,37 +3006,46 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_7</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>idp_NG008019_supp4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3002,32 +3065,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp15</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>idp_NG008019_supp5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3052,27 +3124,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp19</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008019_2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3097,27 +3174,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp23</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008019_4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3132,7 +3214,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3142,27 +3224,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>non_idp_NG008019_6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3187,27 +3274,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp27</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>non_idp_NG008019_7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3222,7 +3314,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3232,27 +3324,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp28</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>non_idp_NG008019_supp15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3267,7 +3364,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tamsum Gamdua</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3277,27 +3374,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>non_idp_NG008019_supp19</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3322,27 +3424,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp33</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>non_idp_NG008019_supp23</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3357,7 +3464,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ajiri</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3367,27 +3474,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp34</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>non_idp_NG008019_supp25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3402,7 +3514,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3412,27 +3524,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG008019_supp35</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>non_idp_NG008019_supp27</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3442,46 +3559,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp1</t>
+          <t>non_idp_NG008019_supp28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3491,46 +3609,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Tamsum Gamdua</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp10</t>
+          <t>non_idp_NG008019_supp3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3540,46 +3659,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp2</t>
+          <t>non_idp_NG008019_supp33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3589,46 +3709,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Ajiri</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp3</t>
+          <t>non_idp_NG008019_supp34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3638,46 +3759,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mobbar</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp4</t>
+          <t>non_idp_NG008019_supp35</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3692,7 +3814,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3702,31 +3824,36 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp5</t>
+          <t>idp_NG008023_supp1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3751,31 +3878,36 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp6</t>
+          <t>idp_NG008023_supp10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3790,7 +3922,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3800,31 +3932,36 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp7</t>
+          <t>idp_NG008023_supp2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>In-host</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3849,31 +3986,36 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp8</t>
+          <t>idp_NG008023_supp3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3888,7 +4030,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3898,31 +4040,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG008023_supp9</t>
+          <t>idp_NG008023_supp4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3942,32 +4089,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>idp_NG008023_supp5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3987,32 +4143,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp11</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>idp_NG008023_supp6</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4032,32 +4197,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp12</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG008023_supp7</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4072,37 +4246,46 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp13</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG008023_supp8</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4122,32 +4305,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp14</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG008023_supp9</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4162,7 +4354,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4172,27 +4364,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp15</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG008023_supp1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4217,27 +4414,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp2</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>non_idp_NG008023_supp11</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4252,7 +4454,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Damasak</t>
+          <t>Zanna Umarti</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4262,27 +4464,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008023_supp12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4307,27 +4514,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp4</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008023_supp13</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4352,27 +4564,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp5</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008023_supp14</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4387,7 +4604,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4397,27 +4614,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp6</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008023_supp15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4442,27 +4664,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp7</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>non_idp_NG008023_supp2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4477,7 +4704,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zanna Umarti</t>
+          <t>Damasak</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4487,45 +4714,300 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008023_supp9</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>non_idp_NG008023_supp3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Zanna Umarti</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>non_idp_NG008023_supp4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zanna Umarti</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>non_idp_NG008023_supp5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Zanna Umarti</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>non_idp_NG008023_supp6</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Zanna Umarti</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>non_idp_NG008023_supp7</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mobbar</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Zanna Umarti</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>non_idp_NG008023_supp9</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4791,13 +5273,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1942002B-AA77-4175-96EC-2664DBAD1F55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F7535E6-7BD6-43FA-8C29-92B4079E16B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{659B56DC-5A79-4EF6-9396-E79D268C02D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87DC2E45-C482-4ECF-884F-305322A6DB9B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B372B483-28C8-4C2A-AEB3-B6334A57C13C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADB4643B-F25B-44E6-87E7-6EFEDAE1EF0D}"/>
 </file>